--- a/subscription_forms/010_snail_mailing_list_request--subscription_forms.xlsx
+++ b/subscription_forms/010_snail_mailing_list_request--subscription_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>email_newsletter</t>
+          <t>email newsletter</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>snail_email</t>
+          <t>snail email</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>snail_and_postcard</t>
+          <t>snail and postcard</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>snail_and_newsletter</t>
+          <t>snail and newsletter</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>snail_and_newsletter_and_postcard</t>
+          <t>snail and newsletter and postcard</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>snail_email_and_postcard</t>
+          <t>snail email and postcard</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>snail_and_email</t>
+          <t>snail and email</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>snail_and_newsletter_and_email</t>
+          <t>snail and newsletter and email</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>snail_and_email_and_postcard</t>
+          <t>snail and email and postcard</t>
         </is>
       </c>
     </row>
@@ -949,24 +949,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>snail_newsletter</t>
+          <t>snail newsletter</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one_1_choices</t>
+          <t>snail_mail_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>snail_and_postcard</t>
+          <t>once_a_year</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>snail_and_postcard</t>
+          <t>once a year</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>once_a_year</t>
+          <t>twice_a_year</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>once_a_year</t>
+          <t>twice a year</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>twice_a_year</t>
+          <t>three_to_four_times_a_year</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>twice_a_year</t>
+          <t>three to four times a year</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>three_to_four_times_a_year</t>
+          <t>five_to_six_times_a_year</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>three_to_four_times_a_year</t>
+          <t>five to six times a year</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>five_to_six_times_a_year</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>five_to_six_times_a_year</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
     </row>
@@ -1097,27 +1097,10 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>snail_mail_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>annually</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>annually</t>
         </is>
